--- a/dbc_signals.xlsx
+++ b/dbc_signals.xlsx
@@ -2889,7 +2889,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K591"/>
+  <dimension ref="A1:K597"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="36" customWidth="1" min="1" max="1"/>
@@ -2900,7 +2900,7 @@
     <col width="8" customWidth="1" min="6" max="6"/>
     <col width="8" customWidth="1" min="7" max="7"/>
     <col width="5" customWidth="1" min="8" max="8"/>
-    <col width="5" customWidth="1" min="9" max="9"/>
+    <col width="7" customWidth="1" min="9" max="9"/>
     <col width="8" customWidth="1" min="10" max="10"/>
     <col width="9" customWidth="1" min="11" max="11"/>
   </cols>
@@ -20689,6 +20689,190 @@
       <c r="I591" s="3" t="n"/>
       <c r="J591" s="3" t="n"/>
       <c r="K591" s="3" t="inlineStr"/>
+    </row>
+    <row r="592"/>
+    <row r="593">
+      <c r="A593" s="1" t="inlineStr">
+        <is>
+          <t>Message: Master_MSC_ID_1</t>
+        </is>
+      </c>
+      <c r="B593" s="1" t="inlineStr">
+        <is>
+          <t>ID: 0x701</t>
+        </is>
+      </c>
+      <c r="C593" s="1" t="inlineStr">
+        <is>
+          <t>Sender(s): AMS</t>
+        </is>
+      </c>
+    </row>
+    <row r="594">
+      <c r="A594" s="2" t="inlineStr">
+        <is>
+          <t>Signal Name</t>
+        </is>
+      </c>
+      <c r="B594" s="2" t="inlineStr">
+        <is>
+          <t>Start Bit</t>
+        </is>
+      </c>
+      <c r="C594" s="2" t="inlineStr">
+        <is>
+          <t>Length (bits)</t>
+        </is>
+      </c>
+      <c r="D594" s="2" t="inlineStr">
+        <is>
+          <t>Byte Order</t>
+        </is>
+      </c>
+      <c r="E594" s="2" t="inlineStr">
+        <is>
+          <t>Signed</t>
+        </is>
+      </c>
+      <c r="F594" s="2" t="inlineStr">
+        <is>
+          <t>Factor</t>
+        </is>
+      </c>
+      <c r="G594" s="2" t="inlineStr">
+        <is>
+          <t>Offset</t>
+        </is>
+      </c>
+      <c r="H594" s="2" t="inlineStr">
+        <is>
+          <t>Min</t>
+        </is>
+      </c>
+      <c r="I594" s="2" t="inlineStr">
+        <is>
+          <t>Max</t>
+        </is>
+      </c>
+      <c r="J594" s="2" t="inlineStr">
+        <is>
+          <t>Unit</t>
+        </is>
+      </c>
+      <c r="K594" s="2" t="inlineStr">
+        <is>
+          <t>Choices</t>
+        </is>
+      </c>
+    </row>
+    <row r="595">
+      <c r="A595" s="3" t="inlineStr">
+        <is>
+          <t>mcu_vref</t>
+        </is>
+      </c>
+      <c r="B595" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="C595" s="3" t="n">
+        <v>8</v>
+      </c>
+      <c r="D595" s="3" t="inlineStr">
+        <is>
+          <t>Intel</t>
+        </is>
+      </c>
+      <c r="E595" s="3" t="b">
+        <v>0</v>
+      </c>
+      <c r="F595" s="3" t="n">
+        <v>0.01</v>
+      </c>
+      <c r="G595" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="H595" s="3" t="n"/>
+      <c r="I595" s="3" t="n"/>
+      <c r="J595" s="3" t="inlineStr">
+        <is>
+          <t>V</t>
+        </is>
+      </c>
+      <c r="K595" s="3" t="inlineStr"/>
+    </row>
+    <row r="596">
+      <c r="A596" s="3" t="inlineStr">
+        <is>
+          <t>mcu_temperature</t>
+        </is>
+      </c>
+      <c r="B596" s="3" t="n">
+        <v>8</v>
+      </c>
+      <c r="C596" s="3" t="n">
+        <v>8</v>
+      </c>
+      <c r="D596" s="3" t="inlineStr">
+        <is>
+          <t>Intel</t>
+        </is>
+      </c>
+      <c r="E596" s="3" t="b">
+        <v>0</v>
+      </c>
+      <c r="F596" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="G596" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="H596" s="3" t="n"/>
+      <c r="I596" s="3" t="n"/>
+      <c r="J596" s="3" t="inlineStr">
+        <is>
+          <t>ºC</t>
+        </is>
+      </c>
+      <c r="K596" s="3" t="inlineStr"/>
+    </row>
+    <row r="597">
+      <c r="A597" s="3" t="inlineStr">
+        <is>
+          <t>ams_current_draw</t>
+        </is>
+      </c>
+      <c r="B597" s="3" t="n">
+        <v>16</v>
+      </c>
+      <c r="C597" s="3" t="n">
+        <v>16</v>
+      </c>
+      <c r="D597" s="3" t="inlineStr">
+        <is>
+          <t>Intel</t>
+        </is>
+      </c>
+      <c r="E597" s="3" t="b">
+        <v>0</v>
+      </c>
+      <c r="F597" s="3" t="n">
+        <v>0.001</v>
+      </c>
+      <c r="G597" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="H597" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="I597" s="3" t="n">
+        <v>65535</v>
+      </c>
+      <c r="J597" s="3" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="K597" s="3" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/dbc_signals.xlsx
+++ b/dbc_signals.xlsx
@@ -20789,7 +20789,7 @@
         <v>0.01</v>
       </c>
       <c r="G595" s="3" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="H595" s="3" t="n"/>
       <c r="I595" s="3" t="n"/>

--- a/dbc_signals.xlsx
+++ b/dbc_signals.xlsx
@@ -2902,7 +2902,7 @@
     <col width="5" customWidth="1" min="8" max="8"/>
     <col width="7" customWidth="1" min="9" max="9"/>
     <col width="8" customWidth="1" min="10" max="10"/>
-    <col width="9" customWidth="1" min="11" max="11"/>
+    <col width="64" customWidth="1" min="11" max="11"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -4185,14 +4185,18 @@
         <v>0</v>
       </c>
       <c r="F42" s="3" t="n">
-        <v>1</v>
+        <v>0.001</v>
       </c>
       <c r="G42" s="3" t="n">
         <v>0</v>
       </c>
       <c r="H42" s="3" t="n"/>
       <c r="I42" s="3" t="n"/>
-      <c r="J42" s="3" t="n"/>
+      <c r="J42" s="3" t="inlineStr">
+        <is>
+          <t>V</t>
+        </is>
+      </c>
       <c r="K42" s="3" t="inlineStr"/>
     </row>
     <row r="43">
@@ -4216,14 +4220,18 @@
         <v>0</v>
       </c>
       <c r="F43" s="3" t="n">
-        <v>1</v>
+        <v>0.001</v>
       </c>
       <c r="G43" s="3" t="n">
         <v>0</v>
       </c>
       <c r="H43" s="3" t="n"/>
       <c r="I43" s="3" t="n"/>
-      <c r="J43" s="3" t="n"/>
+      <c r="J43" s="3" t="inlineStr">
+        <is>
+          <t>V</t>
+        </is>
+      </c>
       <c r="K43" s="3" t="inlineStr"/>
     </row>
     <row r="44">
@@ -4247,14 +4255,18 @@
         <v>0</v>
       </c>
       <c r="F44" s="3" t="n">
-        <v>1</v>
+        <v>0.001</v>
       </c>
       <c r="G44" s="3" t="n">
         <v>0</v>
       </c>
       <c r="H44" s="3" t="n"/>
       <c r="I44" s="3" t="n"/>
-      <c r="J44" s="3" t="n"/>
+      <c r="J44" s="3" t="inlineStr">
+        <is>
+          <t>V</t>
+        </is>
+      </c>
       <c r="K44" s="3" t="inlineStr"/>
     </row>
     <row r="45">
@@ -4278,14 +4290,18 @@
         <v>0</v>
       </c>
       <c r="F45" s="3" t="n">
-        <v>1</v>
+        <v>0.001</v>
       </c>
       <c r="G45" s="3" t="n">
         <v>0</v>
       </c>
       <c r="H45" s="3" t="n"/>
       <c r="I45" s="3" t="n"/>
-      <c r="J45" s="3" t="n"/>
+      <c r="J45" s="3" t="inlineStr">
+        <is>
+          <t>V</t>
+        </is>
+      </c>
       <c r="K45" s="3" t="inlineStr"/>
     </row>
     <row r="46"/>
@@ -4384,14 +4400,18 @@
         <v>0</v>
       </c>
       <c r="F49" s="3" t="n">
-        <v>1</v>
+        <v>0.001</v>
       </c>
       <c r="G49" s="3" t="n">
         <v>0</v>
       </c>
       <c r="H49" s="3" t="n"/>
       <c r="I49" s="3" t="n"/>
-      <c r="J49" s="3" t="n"/>
+      <c r="J49" s="3" t="inlineStr">
+        <is>
+          <t>V</t>
+        </is>
+      </c>
       <c r="K49" s="3" t="inlineStr"/>
     </row>
     <row r="50">
@@ -4415,14 +4435,18 @@
         <v>0</v>
       </c>
       <c r="F50" s="3" t="n">
-        <v>1</v>
+        <v>0.001</v>
       </c>
       <c r="G50" s="3" t="n">
         <v>0</v>
       </c>
       <c r="H50" s="3" t="n"/>
       <c r="I50" s="3" t="n"/>
-      <c r="J50" s="3" t="n"/>
+      <c r="J50" s="3" t="inlineStr">
+        <is>
+          <t>V</t>
+        </is>
+      </c>
       <c r="K50" s="3" t="inlineStr"/>
     </row>
     <row r="51">
@@ -4451,10 +4475,18 @@
       <c r="G51" s="3" t="n">
         <v>0</v>
       </c>
-      <c r="H51" s="3" t="n"/>
-      <c r="I51" s="3" t="n"/>
+      <c r="H51" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="I51" s="3" t="n">
+        <v>1</v>
+      </c>
       <c r="J51" s="3" t="n"/>
-      <c r="K51" s="3" t="inlineStr"/>
+      <c r="K51" s="3" t="inlineStr">
+        <is>
+          <t>0=No fault detected, 1=Cell/open-wire/voltage diagnostic fault</t>
+        </is>
+      </c>
     </row>
     <row r="52">
       <c r="A52" s="3" t="inlineStr">
@@ -4484,7 +4516,11 @@
       </c>
       <c r="H52" s="3" t="n"/>
       <c r="I52" s="3" t="n"/>
-      <c r="J52" s="3" t="n"/>
+      <c r="J52" s="3" t="inlineStr">
+        <is>
+          <t>ºC</t>
+        </is>
+      </c>
       <c r="K52" s="3" t="inlineStr"/>
     </row>
     <row r="53"/>
@@ -5141,7 +5177,7 @@
       </c>
       <c r="B75" s="1" t="inlineStr">
         <is>
-          <t>ID: 0x110</t>
+          <t>ID: 0x10a</t>
         </is>
       </c>
       <c r="C75" s="1" t="inlineStr">
@@ -5356,7 +5392,7 @@
       </c>
       <c r="B82" s="1" t="inlineStr">
         <is>
-          <t>ID: 0x111</t>
+          <t>ID: 0x10b</t>
         </is>
       </c>
       <c r="C82" s="1" t="inlineStr">
@@ -5571,7 +5607,7 @@
       </c>
       <c r="B89" s="1" t="inlineStr">
         <is>
-          <t>ID: 0x112</t>
+          <t>ID: 0x10c</t>
         </is>
       </c>
       <c r="C89" s="1" t="inlineStr">
@@ -5658,14 +5694,18 @@
         <v>0</v>
       </c>
       <c r="F91" s="3" t="n">
-        <v>1</v>
+        <v>0.001</v>
       </c>
       <c r="G91" s="3" t="n">
         <v>0</v>
       </c>
       <c r="H91" s="3" t="n"/>
       <c r="I91" s="3" t="n"/>
-      <c r="J91" s="3" t="n"/>
+      <c r="J91" s="3" t="inlineStr">
+        <is>
+          <t>V</t>
+        </is>
+      </c>
       <c r="K91" s="3" t="inlineStr"/>
     </row>
     <row r="92">
@@ -5689,14 +5729,18 @@
         <v>0</v>
       </c>
       <c r="F92" s="3" t="n">
-        <v>1</v>
+        <v>0.001</v>
       </c>
       <c r="G92" s="3" t="n">
         <v>0</v>
       </c>
       <c r="H92" s="3" t="n"/>
       <c r="I92" s="3" t="n"/>
-      <c r="J92" s="3" t="n"/>
+      <c r="J92" s="3" t="inlineStr">
+        <is>
+          <t>V</t>
+        </is>
+      </c>
       <c r="K92" s="3" t="inlineStr"/>
     </row>
     <row r="93">
@@ -5720,14 +5764,18 @@
         <v>0</v>
       </c>
       <c r="F93" s="3" t="n">
-        <v>1</v>
+        <v>0.001</v>
       </c>
       <c r="G93" s="3" t="n">
         <v>0</v>
       </c>
       <c r="H93" s="3" t="n"/>
       <c r="I93" s="3" t="n"/>
-      <c r="J93" s="3" t="n"/>
+      <c r="J93" s="3" t="inlineStr">
+        <is>
+          <t>V</t>
+        </is>
+      </c>
       <c r="K93" s="3" t="inlineStr"/>
     </row>
     <row r="94">
@@ -5751,14 +5799,18 @@
         <v>0</v>
       </c>
       <c r="F94" s="3" t="n">
-        <v>1</v>
+        <v>0.001</v>
       </c>
       <c r="G94" s="3" t="n">
         <v>0</v>
       </c>
       <c r="H94" s="3" t="n"/>
       <c r="I94" s="3" t="n"/>
-      <c r="J94" s="3" t="n"/>
+      <c r="J94" s="3" t="inlineStr">
+        <is>
+          <t>V</t>
+        </is>
+      </c>
       <c r="K94" s="3" t="inlineStr"/>
     </row>
     <row r="95"/>
@@ -5770,7 +5822,7 @@
       </c>
       <c r="B96" s="1" t="inlineStr">
         <is>
-          <t>ID: 0x113</t>
+          <t>ID: 0x10d</t>
         </is>
       </c>
       <c r="C96" s="1" t="inlineStr">
@@ -5857,14 +5909,18 @@
         <v>0</v>
       </c>
       <c r="F98" s="3" t="n">
-        <v>1</v>
+        <v>0.001</v>
       </c>
       <c r="G98" s="3" t="n">
         <v>0</v>
       </c>
       <c r="H98" s="3" t="n"/>
       <c r="I98" s="3" t="n"/>
-      <c r="J98" s="3" t="n"/>
+      <c r="J98" s="3" t="inlineStr">
+        <is>
+          <t>V</t>
+        </is>
+      </c>
       <c r="K98" s="3" t="inlineStr"/>
     </row>
     <row r="99">
@@ -5888,14 +5944,18 @@
         <v>0</v>
       </c>
       <c r="F99" s="3" t="n">
-        <v>1</v>
+        <v>0.001</v>
       </c>
       <c r="G99" s="3" t="n">
         <v>0</v>
       </c>
       <c r="H99" s="3" t="n"/>
       <c r="I99" s="3" t="n"/>
-      <c r="J99" s="3" t="n"/>
+      <c r="J99" s="3" t="inlineStr">
+        <is>
+          <t>V</t>
+        </is>
+      </c>
       <c r="K99" s="3" t="inlineStr"/>
     </row>
     <row r="100">
@@ -5924,10 +5984,18 @@
       <c r="G100" s="3" t="n">
         <v>0</v>
       </c>
-      <c r="H100" s="3" t="n"/>
-      <c r="I100" s="3" t="n"/>
+      <c r="H100" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="I100" s="3" t="n">
+        <v>1</v>
+      </c>
       <c r="J100" s="3" t="n"/>
-      <c r="K100" s="3" t="inlineStr"/>
+      <c r="K100" s="3" t="inlineStr">
+        <is>
+          <t>0=No fault detected, 1=Cell/open-wire/voltage diagnostic fault</t>
+        </is>
+      </c>
     </row>
     <row r="101">
       <c r="A101" s="3" t="inlineStr">
@@ -5957,7 +6025,11 @@
       </c>
       <c r="H101" s="3" t="n"/>
       <c r="I101" s="3" t="n"/>
-      <c r="J101" s="3" t="n"/>
+      <c r="J101" s="3" t="inlineStr">
+        <is>
+          <t>ºC</t>
+        </is>
+      </c>
       <c r="K101" s="3" t="inlineStr"/>
     </row>
     <row r="102"/>
@@ -5969,7 +6041,7 @@
       </c>
       <c r="B103" s="1" t="inlineStr">
         <is>
-          <t>ID: 0x11a</t>
+          <t>ID: 0x10e</t>
         </is>
       </c>
       <c r="C103" s="1" t="inlineStr">
@@ -6184,7 +6256,7 @@
       </c>
       <c r="B110" s="1" t="inlineStr">
         <is>
-          <t>ID: 0x114</t>
+          <t>ID: 0x10f</t>
         </is>
       </c>
       <c r="C110" s="1" t="inlineStr">
@@ -6399,7 +6471,7 @@
       </c>
       <c r="B117" s="1" t="inlineStr">
         <is>
-          <t>ID: 0x115</t>
+          <t>ID: 0x110</t>
         </is>
       </c>
       <c r="C117" s="1" t="inlineStr">
@@ -6614,7 +6686,7 @@
       </c>
       <c r="B124" s="1" t="inlineStr">
         <is>
-          <t>ID: 0x116</t>
+          <t>ID: 0x111</t>
         </is>
       </c>
       <c r="C124" s="1" t="inlineStr">
@@ -6829,7 +6901,7 @@
       </c>
       <c r="B131" s="1" t="inlineStr">
         <is>
-          <t>ID: 0x117</t>
+          <t>ID: 0x112</t>
         </is>
       </c>
       <c r="C131" s="1" t="inlineStr">
@@ -7044,7 +7116,7 @@
       </c>
       <c r="B138" s="1" t="inlineStr">
         <is>
-          <t>ID: 0x118</t>
+          <t>ID: 0x113</t>
         </is>
       </c>
       <c r="C138" s="1" t="inlineStr">
@@ -7131,14 +7203,18 @@
         <v>0</v>
       </c>
       <c r="F140" s="3" t="n">
-        <v>1</v>
+        <v>0.001</v>
       </c>
       <c r="G140" s="3" t="n">
         <v>0</v>
       </c>
       <c r="H140" s="3" t="n"/>
       <c r="I140" s="3" t="n"/>
-      <c r="J140" s="3" t="n"/>
+      <c r="J140" s="3" t="inlineStr">
+        <is>
+          <t>V</t>
+        </is>
+      </c>
       <c r="K140" s="3" t="inlineStr"/>
     </row>
     <row r="141">
@@ -7162,14 +7238,18 @@
         <v>0</v>
       </c>
       <c r="F141" s="3" t="n">
-        <v>1</v>
+        <v>0.001</v>
       </c>
       <c r="G141" s="3" t="n">
         <v>0</v>
       </c>
       <c r="H141" s="3" t="n"/>
       <c r="I141" s="3" t="n"/>
-      <c r="J141" s="3" t="n"/>
+      <c r="J141" s="3" t="inlineStr">
+        <is>
+          <t>V</t>
+        </is>
+      </c>
       <c r="K141" s="3" t="inlineStr"/>
     </row>
     <row r="142">
@@ -7193,14 +7273,18 @@
         <v>0</v>
       </c>
       <c r="F142" s="3" t="n">
-        <v>1</v>
+        <v>0.001</v>
       </c>
       <c r="G142" s="3" t="n">
         <v>0</v>
       </c>
       <c r="H142" s="3" t="n"/>
       <c r="I142" s="3" t="n"/>
-      <c r="J142" s="3" t="n"/>
+      <c r="J142" s="3" t="inlineStr">
+        <is>
+          <t>V</t>
+        </is>
+      </c>
       <c r="K142" s="3" t="inlineStr"/>
     </row>
     <row r="143">
@@ -7224,14 +7308,18 @@
         <v>0</v>
       </c>
       <c r="F143" s="3" t="n">
-        <v>1</v>
+        <v>0.001</v>
       </c>
       <c r="G143" s="3" t="n">
         <v>0</v>
       </c>
       <c r="H143" s="3" t="n"/>
       <c r="I143" s="3" t="n"/>
-      <c r="J143" s="3" t="n"/>
+      <c r="J143" s="3" t="inlineStr">
+        <is>
+          <t>V</t>
+        </is>
+      </c>
       <c r="K143" s="3" t="inlineStr"/>
     </row>
     <row r="144"/>
@@ -7243,7 +7331,7 @@
       </c>
       <c r="B145" s="1" t="inlineStr">
         <is>
-          <t>ID: 0x119</t>
+          <t>ID: 0x114</t>
         </is>
       </c>
       <c r="C145" s="1" t="inlineStr">
@@ -7330,14 +7418,18 @@
         <v>0</v>
       </c>
       <c r="F147" s="3" t="n">
-        <v>1</v>
+        <v>0.001</v>
       </c>
       <c r="G147" s="3" t="n">
         <v>0</v>
       </c>
       <c r="H147" s="3" t="n"/>
       <c r="I147" s="3" t="n"/>
-      <c r="J147" s="3" t="n"/>
+      <c r="J147" s="3" t="inlineStr">
+        <is>
+          <t>V</t>
+        </is>
+      </c>
       <c r="K147" s="3" t="inlineStr"/>
     </row>
     <row r="148">
@@ -7361,14 +7453,18 @@
         <v>0</v>
       </c>
       <c r="F148" s="3" t="n">
-        <v>1</v>
+        <v>0.001</v>
       </c>
       <c r="G148" s="3" t="n">
         <v>0</v>
       </c>
       <c r="H148" s="3" t="n"/>
       <c r="I148" s="3" t="n"/>
-      <c r="J148" s="3" t="n"/>
+      <c r="J148" s="3" t="inlineStr">
+        <is>
+          <t>V</t>
+        </is>
+      </c>
       <c r="K148" s="3" t="inlineStr"/>
     </row>
     <row r="149">
@@ -7397,10 +7493,18 @@
       <c r="G149" s="3" t="n">
         <v>0</v>
       </c>
-      <c r="H149" s="3" t="n"/>
-      <c r="I149" s="3" t="n"/>
+      <c r="H149" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="I149" s="3" t="n">
+        <v>1</v>
+      </c>
       <c r="J149" s="3" t="n"/>
-      <c r="K149" s="3" t="inlineStr"/>
+      <c r="K149" s="3" t="inlineStr">
+        <is>
+          <t>0=No fault detected, 1=Cell/open-wire/voltage diagnostic fault</t>
+        </is>
+      </c>
     </row>
     <row r="150">
       <c r="A150" s="3" t="inlineStr">
@@ -7430,7 +7534,11 @@
       </c>
       <c r="H150" s="3" t="n"/>
       <c r="I150" s="3" t="n"/>
-      <c r="J150" s="3" t="n"/>
+      <c r="J150" s="3" t="inlineStr">
+        <is>
+          <t>ºC</t>
+        </is>
+      </c>
       <c r="K150" s="3" t="inlineStr"/>
     </row>
     <row r="151"/>
@@ -7442,7 +7550,7 @@
       </c>
       <c r="B152" s="1" t="inlineStr">
         <is>
-          <t>ID: 0x120</t>
+          <t>ID: 0x115</t>
         </is>
       </c>
       <c r="C152" s="1" t="inlineStr">
@@ -7657,7 +7765,7 @@
       </c>
       <c r="B159" s="1" t="inlineStr">
         <is>
-          <t>ID: 0x121</t>
+          <t>ID: 0x116</t>
         </is>
       </c>
       <c r="C159" s="1" t="inlineStr">
@@ -7872,7 +7980,7 @@
       </c>
       <c r="B166" s="1" t="inlineStr">
         <is>
-          <t>ID: 0x122</t>
+          <t>ID: 0x117</t>
         </is>
       </c>
       <c r="C166" s="1" t="inlineStr">
@@ -8087,7 +8195,7 @@
       </c>
       <c r="B173" s="1" t="inlineStr">
         <is>
-          <t>ID: 0x123</t>
+          <t>ID: 0x118</t>
         </is>
       </c>
       <c r="C173" s="1" t="inlineStr">
@@ -8302,7 +8410,7 @@
       </c>
       <c r="B180" s="1" t="inlineStr">
         <is>
-          <t>ID: 0x124</t>
+          <t>ID: 0x119</t>
         </is>
       </c>
       <c r="C180" s="1" t="inlineStr">
@@ -8517,7 +8625,7 @@
       </c>
       <c r="B187" s="1" t="inlineStr">
         <is>
-          <t>ID: 0x125</t>
+          <t>ID: 0x11a</t>
         </is>
       </c>
       <c r="C187" s="1" t="inlineStr">
@@ -8604,14 +8712,18 @@
         <v>0</v>
       </c>
       <c r="F189" s="3" t="n">
-        <v>1</v>
+        <v>0.001</v>
       </c>
       <c r="G189" s="3" t="n">
         <v>0</v>
       </c>
       <c r="H189" s="3" t="n"/>
       <c r="I189" s="3" t="n"/>
-      <c r="J189" s="3" t="n"/>
+      <c r="J189" s="3" t="inlineStr">
+        <is>
+          <t>V</t>
+        </is>
+      </c>
       <c r="K189" s="3" t="inlineStr"/>
     </row>
     <row r="190">
@@ -8635,14 +8747,18 @@
         <v>0</v>
       </c>
       <c r="F190" s="3" t="n">
-        <v>1</v>
+        <v>0.001</v>
       </c>
       <c r="G190" s="3" t="n">
         <v>0</v>
       </c>
       <c r="H190" s="3" t="n"/>
       <c r="I190" s="3" t="n"/>
-      <c r="J190" s="3" t="n"/>
+      <c r="J190" s="3" t="inlineStr">
+        <is>
+          <t>V</t>
+        </is>
+      </c>
       <c r="K190" s="3" t="inlineStr"/>
     </row>
     <row r="191">
@@ -8666,14 +8782,18 @@
         <v>0</v>
       </c>
       <c r="F191" s="3" t="n">
-        <v>1</v>
+        <v>0.001</v>
       </c>
       <c r="G191" s="3" t="n">
         <v>0</v>
       </c>
       <c r="H191" s="3" t="n"/>
       <c r="I191" s="3" t="n"/>
-      <c r="J191" s="3" t="n"/>
+      <c r="J191" s="3" t="inlineStr">
+        <is>
+          <t>V</t>
+        </is>
+      </c>
       <c r="K191" s="3" t="inlineStr"/>
     </row>
     <row r="192">
@@ -8697,14 +8817,18 @@
         <v>0</v>
       </c>
       <c r="F192" s="3" t="n">
-        <v>1</v>
+        <v>0.001</v>
       </c>
       <c r="G192" s="3" t="n">
         <v>0</v>
       </c>
       <c r="H192" s="3" t="n"/>
       <c r="I192" s="3" t="n"/>
-      <c r="J192" s="3" t="n"/>
+      <c r="J192" s="3" t="inlineStr">
+        <is>
+          <t>V</t>
+        </is>
+      </c>
       <c r="K192" s="3" t="inlineStr"/>
     </row>
     <row r="193"/>
@@ -8716,7 +8840,7 @@
       </c>
       <c r="B194" s="1" t="inlineStr">
         <is>
-          <t>ID: 0x126</t>
+          <t>ID: 0x11b</t>
         </is>
       </c>
       <c r="C194" s="1" t="inlineStr">
@@ -8803,14 +8927,18 @@
         <v>0</v>
       </c>
       <c r="F196" s="3" t="n">
-        <v>1</v>
+        <v>0.001</v>
       </c>
       <c r="G196" s="3" t="n">
         <v>0</v>
       </c>
       <c r="H196" s="3" t="n"/>
       <c r="I196" s="3" t="n"/>
-      <c r="J196" s="3" t="n"/>
+      <c r="J196" s="3" t="inlineStr">
+        <is>
+          <t>V</t>
+        </is>
+      </c>
       <c r="K196" s="3" t="inlineStr"/>
     </row>
     <row r="197">
@@ -8834,14 +8962,18 @@
         <v>0</v>
       </c>
       <c r="F197" s="3" t="n">
-        <v>1</v>
+        <v>0.001</v>
       </c>
       <c r="G197" s="3" t="n">
         <v>0</v>
       </c>
       <c r="H197" s="3" t="n"/>
       <c r="I197" s="3" t="n"/>
-      <c r="J197" s="3" t="n"/>
+      <c r="J197" s="3" t="inlineStr">
+        <is>
+          <t>V</t>
+        </is>
+      </c>
       <c r="K197" s="3" t="inlineStr"/>
     </row>
     <row r="198">
@@ -8870,10 +9002,18 @@
       <c r="G198" s="3" t="n">
         <v>0</v>
       </c>
-      <c r="H198" s="3" t="n"/>
-      <c r="I198" s="3" t="n"/>
+      <c r="H198" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="I198" s="3" t="n">
+        <v>1</v>
+      </c>
       <c r="J198" s="3" t="n"/>
-      <c r="K198" s="3" t="inlineStr"/>
+      <c r="K198" s="3" t="inlineStr">
+        <is>
+          <t>0=No fault detected, 1=Cell/open-wire/voltage diagnostic fault</t>
+        </is>
+      </c>
     </row>
     <row r="199">
       <c r="A199" s="3" t="inlineStr">
@@ -8903,7 +9043,11 @@
       </c>
       <c r="H199" s="3" t="n"/>
       <c r="I199" s="3" t="n"/>
-      <c r="J199" s="3" t="n"/>
+      <c r="J199" s="3" t="inlineStr">
+        <is>
+          <t>ºC</t>
+        </is>
+      </c>
       <c r="K199" s="3" t="inlineStr"/>
     </row>
     <row r="200"/>
@@ -8915,7 +9059,7 @@
       </c>
       <c r="B201" s="1" t="inlineStr">
         <is>
-          <t>ID: 0x127</t>
+          <t>ID: 0x11c</t>
         </is>
       </c>
       <c r="C201" s="1" t="inlineStr">
@@ -9130,7 +9274,7 @@
       </c>
       <c r="B208" s="1" t="inlineStr">
         <is>
-          <t>ID: 0x128</t>
+          <t>ID: 0x11d</t>
         </is>
       </c>
       <c r="C208" s="1" t="inlineStr">
@@ -9345,7 +9489,7 @@
       </c>
       <c r="B215" s="1" t="inlineStr">
         <is>
-          <t>ID: 0x129</t>
+          <t>ID: 0x11e</t>
         </is>
       </c>
       <c r="C215" s="1" t="inlineStr">
@@ -9560,7 +9704,7 @@
       </c>
       <c r="B222" s="1" t="inlineStr">
         <is>
-          <t>ID: 0x130</t>
+          <t>ID: 0x11f</t>
         </is>
       </c>
       <c r="C222" s="1" t="inlineStr">
@@ -9775,7 +9919,7 @@
       </c>
       <c r="B229" s="1" t="inlineStr">
         <is>
-          <t>ID: 0x131</t>
+          <t>ID: 0x120</t>
         </is>
       </c>
       <c r="C229" s="1" t="inlineStr">
@@ -9990,7 +10134,7 @@
       </c>
       <c r="B236" s="1" t="inlineStr">
         <is>
-          <t>ID: 0x132</t>
+          <t>ID: 0x121</t>
         </is>
       </c>
       <c r="C236" s="1" t="inlineStr">
@@ -10077,14 +10221,18 @@
         <v>0</v>
       </c>
       <c r="F238" s="3" t="n">
-        <v>1</v>
+        <v>0.001</v>
       </c>
       <c r="G238" s="3" t="n">
         <v>0</v>
       </c>
       <c r="H238" s="3" t="n"/>
       <c r="I238" s="3" t="n"/>
-      <c r="J238" s="3" t="n"/>
+      <c r="J238" s="3" t="inlineStr">
+        <is>
+          <t>V</t>
+        </is>
+      </c>
       <c r="K238" s="3" t="inlineStr"/>
     </row>
     <row r="239">
@@ -10108,14 +10256,18 @@
         <v>0</v>
       </c>
       <c r="F239" s="3" t="n">
-        <v>1</v>
+        <v>0.001</v>
       </c>
       <c r="G239" s="3" t="n">
         <v>0</v>
       </c>
       <c r="H239" s="3" t="n"/>
       <c r="I239" s="3" t="n"/>
-      <c r="J239" s="3" t="n"/>
+      <c r="J239" s="3" t="inlineStr">
+        <is>
+          <t>V</t>
+        </is>
+      </c>
       <c r="K239" s="3" t="inlineStr"/>
     </row>
     <row r="240">
@@ -10139,14 +10291,18 @@
         <v>0</v>
       </c>
       <c r="F240" s="3" t="n">
-        <v>1</v>
+        <v>0.001</v>
       </c>
       <c r="G240" s="3" t="n">
         <v>0</v>
       </c>
       <c r="H240" s="3" t="n"/>
       <c r="I240" s="3" t="n"/>
-      <c r="J240" s="3" t="n"/>
+      <c r="J240" s="3" t="inlineStr">
+        <is>
+          <t>V</t>
+        </is>
+      </c>
       <c r="K240" s="3" t="inlineStr"/>
     </row>
     <row r="241">
@@ -10170,14 +10326,18 @@
         <v>0</v>
       </c>
       <c r="F241" s="3" t="n">
-        <v>1</v>
+        <v>0.001</v>
       </c>
       <c r="G241" s="3" t="n">
         <v>0</v>
       </c>
       <c r="H241" s="3" t="n"/>
       <c r="I241" s="3" t="n"/>
-      <c r="J241" s="3" t="n"/>
+      <c r="J241" s="3" t="inlineStr">
+        <is>
+          <t>V</t>
+        </is>
+      </c>
       <c r="K241" s="3" t="inlineStr"/>
     </row>
     <row r="242"/>
@@ -10189,7 +10349,7 @@
       </c>
       <c r="B243" s="1" t="inlineStr">
         <is>
-          <t>ID: 0x133</t>
+          <t>ID: 0x122</t>
         </is>
       </c>
       <c r="C243" s="1" t="inlineStr">
@@ -10276,14 +10436,18 @@
         <v>0</v>
       </c>
       <c r="F245" s="3" t="n">
-        <v>1</v>
+        <v>0.001</v>
       </c>
       <c r="G245" s="3" t="n">
         <v>0</v>
       </c>
       <c r="H245" s="3" t="n"/>
       <c r="I245" s="3" t="n"/>
-      <c r="J245" s="3" t="n"/>
+      <c r="J245" s="3" t="inlineStr">
+        <is>
+          <t>V</t>
+        </is>
+      </c>
       <c r="K245" s="3" t="inlineStr"/>
     </row>
     <row r="246">
@@ -10307,14 +10471,18 @@
         <v>0</v>
       </c>
       <c r="F246" s="3" t="n">
-        <v>1</v>
+        <v>0.001</v>
       </c>
       <c r="G246" s="3" t="n">
         <v>0</v>
       </c>
       <c r="H246" s="3" t="n"/>
       <c r="I246" s="3" t="n"/>
-      <c r="J246" s="3" t="n"/>
+      <c r="J246" s="3" t="inlineStr">
+        <is>
+          <t>V</t>
+        </is>
+      </c>
       <c r="K246" s="3" t="inlineStr"/>
     </row>
     <row r="247">
@@ -10343,10 +10511,18 @@
       <c r="G247" s="3" t="n">
         <v>0</v>
       </c>
-      <c r="H247" s="3" t="n"/>
-      <c r="I247" s="3" t="n"/>
+      <c r="H247" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="I247" s="3" t="n">
+        <v>1</v>
+      </c>
       <c r="J247" s="3" t="n"/>
-      <c r="K247" s="3" t="inlineStr"/>
+      <c r="K247" s="3" t="inlineStr">
+        <is>
+          <t>0=No fault detected, 1=Cell/open-wire/voltage diagnostic fault</t>
+        </is>
+      </c>
     </row>
     <row r="248">
       <c r="A248" s="3" t="inlineStr">
@@ -10376,7 +10552,11 @@
       </c>
       <c r="H248" s="3" t="n"/>
       <c r="I248" s="3" t="n"/>
-      <c r="J248" s="3" t="n"/>
+      <c r="J248" s="3" t="inlineStr">
+        <is>
+          <t>ºC</t>
+        </is>
+      </c>
       <c r="K248" s="3" t="inlineStr"/>
     </row>
     <row r="249"/>
@@ -10388,7 +10568,7 @@
       </c>
       <c r="B250" s="1" t="inlineStr">
         <is>
-          <t>ID: 0x134</t>
+          <t>ID: 0x123</t>
         </is>
       </c>
       <c r="C250" s="1" t="inlineStr">
@@ -10603,7 +10783,7 @@
       </c>
       <c r="B257" s="1" t="inlineStr">
         <is>
-          <t>ID: 0x135</t>
+          <t>ID: 0x124</t>
         </is>
       </c>
       <c r="C257" s="1" t="inlineStr">
@@ -10818,7 +10998,7 @@
       </c>
       <c r="B264" s="1" t="inlineStr">
         <is>
-          <t>ID: 0x136</t>
+          <t>ID: 0x125</t>
         </is>
       </c>
       <c r="C264" s="1" t="inlineStr">
@@ -11033,7 +11213,7 @@
       </c>
       <c r="B271" s="1" t="inlineStr">
         <is>
-          <t>ID: 0x137</t>
+          <t>ID: 0x126</t>
         </is>
       </c>
       <c r="C271" s="1" t="inlineStr">
@@ -11248,7 +11428,7 @@
       </c>
       <c r="B278" s="1" t="inlineStr">
         <is>
-          <t>ID: 0x138</t>
+          <t>ID: 0x127</t>
         </is>
       </c>
       <c r="C278" s="1" t="inlineStr">
@@ -11463,7 +11643,7 @@
       </c>
       <c r="B285" s="1" t="inlineStr">
         <is>
-          <t>ID: 0x139</t>
+          <t>ID: 0x128</t>
         </is>
       </c>
       <c r="C285" s="1" t="inlineStr">
@@ -11550,14 +11730,18 @@
         <v>0</v>
       </c>
       <c r="F287" s="3" t="n">
-        <v>1</v>
+        <v>0.001</v>
       </c>
       <c r="G287" s="3" t="n">
         <v>0</v>
       </c>
       <c r="H287" s="3" t="n"/>
       <c r="I287" s="3" t="n"/>
-      <c r="J287" s="3" t="n"/>
+      <c r="J287" s="3" t="inlineStr">
+        <is>
+          <t>V</t>
+        </is>
+      </c>
       <c r="K287" s="3" t="inlineStr"/>
     </row>
     <row r="288">
@@ -11581,14 +11765,18 @@
         <v>0</v>
       </c>
       <c r="F288" s="3" t="n">
-        <v>1</v>
+        <v>0.001</v>
       </c>
       <c r="G288" s="3" t="n">
         <v>0</v>
       </c>
       <c r="H288" s="3" t="n"/>
       <c r="I288" s="3" t="n"/>
-      <c r="J288" s="3" t="n"/>
+      <c r="J288" s="3" t="inlineStr">
+        <is>
+          <t>V</t>
+        </is>
+      </c>
       <c r="K288" s="3" t="inlineStr"/>
     </row>
     <row r="289">
@@ -11612,14 +11800,18 @@
         <v>0</v>
       </c>
       <c r="F289" s="3" t="n">
-        <v>1</v>
+        <v>0.001</v>
       </c>
       <c r="G289" s="3" t="n">
         <v>0</v>
       </c>
       <c r="H289" s="3" t="n"/>
       <c r="I289" s="3" t="n"/>
-      <c r="J289" s="3" t="n"/>
+      <c r="J289" s="3" t="inlineStr">
+        <is>
+          <t>V</t>
+        </is>
+      </c>
       <c r="K289" s="3" t="inlineStr"/>
     </row>
     <row r="290">
@@ -11643,14 +11835,18 @@
         <v>0</v>
       </c>
       <c r="F290" s="3" t="n">
-        <v>1</v>
+        <v>0.001</v>
       </c>
       <c r="G290" s="3" t="n">
         <v>0</v>
       </c>
       <c r="H290" s="3" t="n"/>
       <c r="I290" s="3" t="n"/>
-      <c r="J290" s="3" t="n"/>
+      <c r="J290" s="3" t="inlineStr">
+        <is>
+          <t>V</t>
+        </is>
+      </c>
       <c r="K290" s="3" t="inlineStr"/>
     </row>
     <row r="291"/>
@@ -11662,7 +11858,7 @@
       </c>
       <c r="B292" s="1" t="inlineStr">
         <is>
-          <t>ID: 0x140</t>
+          <t>ID: 0x129</t>
         </is>
       </c>
       <c r="C292" s="1" t="inlineStr">
@@ -11749,14 +11945,18 @@
         <v>0</v>
       </c>
       <c r="F294" s="3" t="n">
-        <v>1</v>
+        <v>0.001</v>
       </c>
       <c r="G294" s="3" t="n">
         <v>0</v>
       </c>
       <c r="H294" s="3" t="n"/>
       <c r="I294" s="3" t="n"/>
-      <c r="J294" s="3" t="n"/>
+      <c r="J294" s="3" t="inlineStr">
+        <is>
+          <t>V</t>
+        </is>
+      </c>
       <c r="K294" s="3" t="inlineStr"/>
     </row>
     <row r="295">
@@ -11780,14 +11980,18 @@
         <v>0</v>
       </c>
       <c r="F295" s="3" t="n">
-        <v>1</v>
+        <v>0.001</v>
       </c>
       <c r="G295" s="3" t="n">
         <v>0</v>
       </c>
       <c r="H295" s="3" t="n"/>
       <c r="I295" s="3" t="n"/>
-      <c r="J295" s="3" t="n"/>
+      <c r="J295" s="3" t="inlineStr">
+        <is>
+          <t>V</t>
+        </is>
+      </c>
       <c r="K295" s="3" t="inlineStr"/>
     </row>
     <row r="296">
@@ -11816,10 +12020,18 @@
       <c r="G296" s="3" t="n">
         <v>0</v>
       </c>
-      <c r="H296" s="3" t="n"/>
-      <c r="I296" s="3" t="n"/>
+      <c r="H296" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="I296" s="3" t="n">
+        <v>1</v>
+      </c>
       <c r="J296" s="3" t="n"/>
-      <c r="K296" s="3" t="inlineStr"/>
+      <c r="K296" s="3" t="inlineStr">
+        <is>
+          <t>0=No fault detected, 1=Cell/open-wire/voltage diagnostic fault</t>
+        </is>
+      </c>
     </row>
     <row r="297">
       <c r="A297" s="3" t="inlineStr">
@@ -11849,7 +12061,11 @@
       </c>
       <c r="H297" s="3" t="n"/>
       <c r="I297" s="3" t="n"/>
-      <c r="J297" s="3" t="n"/>
+      <c r="J297" s="3" t="inlineStr">
+        <is>
+          <t>ºC</t>
+        </is>
+      </c>
       <c r="K297" s="3" t="inlineStr"/>
     </row>
     <row r="298"/>
@@ -11861,7 +12077,7 @@
       </c>
       <c r="B299" s="1" t="inlineStr">
         <is>
-          <t>ID: 0x141</t>
+          <t>ID: 0x12a</t>
         </is>
       </c>
       <c r="C299" s="1" t="inlineStr">
@@ -12076,7 +12292,7 @@
       </c>
       <c r="B306" s="1" t="inlineStr">
         <is>
-          <t>ID: 0x142</t>
+          <t>ID: 0x12b</t>
         </is>
       </c>
       <c r="C306" s="1" t="inlineStr">
@@ -12291,7 +12507,7 @@
       </c>
       <c r="B313" s="1" t="inlineStr">
         <is>
-          <t>ID: 0x143</t>
+          <t>ID: 0x12c</t>
         </is>
       </c>
       <c r="C313" s="1" t="inlineStr">
@@ -12506,7 +12722,7 @@
       </c>
       <c r="B320" s="1" t="inlineStr">
         <is>
-          <t>ID: 0x144</t>
+          <t>ID: 0x12d</t>
         </is>
       </c>
       <c r="C320" s="1" t="inlineStr">
@@ -12721,7 +12937,7 @@
       </c>
       <c r="B327" s="1" t="inlineStr">
         <is>
-          <t>ID: 0x145</t>
+          <t>ID: 0x12e</t>
         </is>
       </c>
       <c r="C327" s="1" t="inlineStr">
@@ -12936,7 +13152,7 @@
       </c>
       <c r="B334" s="1" t="inlineStr">
         <is>
-          <t>ID: 0x146</t>
+          <t>ID: 0x12f</t>
         </is>
       </c>
       <c r="C334" s="1" t="inlineStr">
@@ -13023,14 +13239,18 @@
         <v>0</v>
       </c>
       <c r="F336" s="3" t="n">
-        <v>1</v>
+        <v>0.001</v>
       </c>
       <c r="G336" s="3" t="n">
         <v>0</v>
       </c>
       <c r="H336" s="3" t="n"/>
       <c r="I336" s="3" t="n"/>
-      <c r="J336" s="3" t="n"/>
+      <c r="J336" s="3" t="inlineStr">
+        <is>
+          <t>V</t>
+        </is>
+      </c>
       <c r="K336" s="3" t="inlineStr"/>
     </row>
     <row r="337">
@@ -13054,14 +13274,18 @@
         <v>0</v>
       </c>
       <c r="F337" s="3" t="n">
-        <v>1</v>
+        <v>0.001</v>
       </c>
       <c r="G337" s="3" t="n">
         <v>0</v>
       </c>
       <c r="H337" s="3" t="n"/>
       <c r="I337" s="3" t="n"/>
-      <c r="J337" s="3" t="n"/>
+      <c r="J337" s="3" t="inlineStr">
+        <is>
+          <t>V</t>
+        </is>
+      </c>
       <c r="K337" s="3" t="inlineStr"/>
     </row>
     <row r="338">
@@ -13085,14 +13309,18 @@
         <v>0</v>
       </c>
       <c r="F338" s="3" t="n">
-        <v>1</v>
+        <v>0.001</v>
       </c>
       <c r="G338" s="3" t="n">
         <v>0</v>
       </c>
       <c r="H338" s="3" t="n"/>
       <c r="I338" s="3" t="n"/>
-      <c r="J338" s="3" t="n"/>
+      <c r="J338" s="3" t="inlineStr">
+        <is>
+          <t>V</t>
+        </is>
+      </c>
       <c r="K338" s="3" t="inlineStr"/>
     </row>
     <row r="339">
@@ -13116,14 +13344,18 @@
         <v>0</v>
       </c>
       <c r="F339" s="3" t="n">
-        <v>1</v>
+        <v>0.001</v>
       </c>
       <c r="G339" s="3" t="n">
         <v>0</v>
       </c>
       <c r="H339" s="3" t="n"/>
       <c r="I339" s="3" t="n"/>
-      <c r="J339" s="3" t="n"/>
+      <c r="J339" s="3" t="inlineStr">
+        <is>
+          <t>V</t>
+        </is>
+      </c>
       <c r="K339" s="3" t="inlineStr"/>
     </row>
     <row r="340"/>
@@ -13135,7 +13367,7 @@
       </c>
       <c r="B341" s="1" t="inlineStr">
         <is>
-          <t>ID: 0x147</t>
+          <t>ID: 0x130</t>
         </is>
       </c>
       <c r="C341" s="1" t="inlineStr">
@@ -13222,14 +13454,18 @@
         <v>0</v>
       </c>
       <c r="F343" s="3" t="n">
-        <v>1</v>
+        <v>0.001</v>
       </c>
       <c r="G343" s="3" t="n">
         <v>0</v>
       </c>
       <c r="H343" s="3" t="n"/>
       <c r="I343" s="3" t="n"/>
-      <c r="J343" s="3" t="n"/>
+      <c r="J343" s="3" t="inlineStr">
+        <is>
+          <t>V</t>
+        </is>
+      </c>
       <c r="K343" s="3" t="inlineStr"/>
     </row>
     <row r="344">
@@ -13253,14 +13489,18 @@
         <v>0</v>
       </c>
       <c r="F344" s="3" t="n">
-        <v>1</v>
+        <v>0.001</v>
       </c>
       <c r="G344" s="3" t="n">
         <v>0</v>
       </c>
       <c r="H344" s="3" t="n"/>
       <c r="I344" s="3" t="n"/>
-      <c r="J344" s="3" t="n"/>
+      <c r="J344" s="3" t="inlineStr">
+        <is>
+          <t>V</t>
+        </is>
+      </c>
       <c r="K344" s="3" t="inlineStr"/>
     </row>
     <row r="345">
@@ -13289,10 +13529,18 @@
       <c r="G345" s="3" t="n">
         <v>0</v>
       </c>
-      <c r="H345" s="3" t="n"/>
-      <c r="I345" s="3" t="n"/>
+      <c r="H345" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="I345" s="3" t="n">
+        <v>1</v>
+      </c>
       <c r="J345" s="3" t="n"/>
-      <c r="K345" s="3" t="inlineStr"/>
+      <c r="K345" s="3" t="inlineStr">
+        <is>
+          <t>0=No fault detected, 1=Cell/open-wire/voltage diagnostic fault</t>
+        </is>
+      </c>
     </row>
     <row r="346">
       <c r="A346" s="3" t="inlineStr">
@@ -13322,7 +13570,11 @@
       </c>
       <c r="H346" s="3" t="n"/>
       <c r="I346" s="3" t="n"/>
-      <c r="J346" s="3" t="n"/>
+      <c r="J346" s="3" t="inlineStr">
+        <is>
+          <t>ºC</t>
+        </is>
+      </c>
       <c r="K346" s="3" t="inlineStr"/>
     </row>
     <row r="347"/>
@@ -13334,7 +13586,7 @@
       </c>
       <c r="B348" s="1" t="inlineStr">
         <is>
-          <t>ID: 0x148</t>
+          <t>ID: 0x131</t>
         </is>
       </c>
       <c r="C348" s="1" t="inlineStr">
@@ -13549,7 +13801,7 @@
       </c>
       <c r="B355" s="1" t="inlineStr">
         <is>
-          <t>ID: 0x149</t>
+          <t>ID: 0x132</t>
         </is>
       </c>
       <c r="C355" s="1" t="inlineStr">
@@ -13764,7 +14016,7 @@
       </c>
       <c r="B362" s="1" t="inlineStr">
         <is>
-          <t>ID: 0x150</t>
+          <t>ID: 0x133</t>
         </is>
       </c>
       <c r="C362" s="1" t="inlineStr">
@@ -13979,7 +14231,7 @@
       </c>
       <c r="B369" s="1" t="inlineStr">
         <is>
-          <t>ID: 0x151</t>
+          <t>ID: 0x134</t>
         </is>
       </c>
       <c r="C369" s="1" t="inlineStr">
@@ -14194,7 +14446,7 @@
       </c>
       <c r="B376" s="1" t="inlineStr">
         <is>
-          <t>ID: 0x152</t>
+          <t>ID: 0x135</t>
         </is>
       </c>
       <c r="C376" s="1" t="inlineStr">
@@ -14409,7 +14661,7 @@
       </c>
       <c r="B383" s="1" t="inlineStr">
         <is>
-          <t>ID: 0x153</t>
+          <t>ID: 0x136</t>
         </is>
       </c>
       <c r="C383" s="1" t="inlineStr">
@@ -14496,14 +14748,18 @@
         <v>0</v>
       </c>
       <c r="F385" s="3" t="n">
-        <v>1</v>
+        <v>0.001</v>
       </c>
       <c r="G385" s="3" t="n">
         <v>0</v>
       </c>
       <c r="H385" s="3" t="n"/>
       <c r="I385" s="3" t="n"/>
-      <c r="J385" s="3" t="n"/>
+      <c r="J385" s="3" t="inlineStr">
+        <is>
+          <t>V</t>
+        </is>
+      </c>
       <c r="K385" s="3" t="inlineStr"/>
     </row>
     <row r="386">
@@ -14527,14 +14783,18 @@
         <v>0</v>
       </c>
       <c r="F386" s="3" t="n">
-        <v>1</v>
+        <v>0.001</v>
       </c>
       <c r="G386" s="3" t="n">
         <v>0</v>
       </c>
       <c r="H386" s="3" t="n"/>
       <c r="I386" s="3" t="n"/>
-      <c r="J386" s="3" t="n"/>
+      <c r="J386" s="3" t="inlineStr">
+        <is>
+          <t>V</t>
+        </is>
+      </c>
       <c r="K386" s="3" t="inlineStr"/>
     </row>
     <row r="387">
@@ -14558,14 +14818,18 @@
         <v>0</v>
       </c>
       <c r="F387" s="3" t="n">
-        <v>1</v>
+        <v>0.001</v>
       </c>
       <c r="G387" s="3" t="n">
         <v>0</v>
       </c>
       <c r="H387" s="3" t="n"/>
       <c r="I387" s="3" t="n"/>
-      <c r="J387" s="3" t="n"/>
+      <c r="J387" s="3" t="inlineStr">
+        <is>
+          <t>V</t>
+        </is>
+      </c>
       <c r="K387" s="3" t="inlineStr"/>
     </row>
     <row r="388">
@@ -14589,14 +14853,18 @@
         <v>0</v>
       </c>
       <c r="F388" s="3" t="n">
-        <v>1</v>
+        <v>0.001</v>
       </c>
       <c r="G388" s="3" t="n">
         <v>0</v>
       </c>
       <c r="H388" s="3" t="n"/>
       <c r="I388" s="3" t="n"/>
-      <c r="J388" s="3" t="n"/>
+      <c r="J388" s="3" t="inlineStr">
+        <is>
+          <t>V</t>
+        </is>
+      </c>
       <c r="K388" s="3" t="inlineStr"/>
     </row>
     <row r="389"/>
@@ -14608,7 +14876,7 @@
       </c>
       <c r="B390" s="1" t="inlineStr">
         <is>
-          <t>ID: 0x154</t>
+          <t>ID: 0x137</t>
         </is>
       </c>
       <c r="C390" s="1" t="inlineStr">
@@ -14695,14 +14963,18 @@
         <v>0</v>
       </c>
       <c r="F392" s="3" t="n">
-        <v>1</v>
+        <v>0.001</v>
       </c>
       <c r="G392" s="3" t="n">
         <v>0</v>
       </c>
       <c r="H392" s="3" t="n"/>
       <c r="I392" s="3" t="n"/>
-      <c r="J392" s="3" t="n"/>
+      <c r="J392" s="3" t="inlineStr">
+        <is>
+          <t>V</t>
+        </is>
+      </c>
       <c r="K392" s="3" t="inlineStr"/>
     </row>
     <row r="393">
@@ -14726,14 +14998,18 @@
         <v>0</v>
       </c>
       <c r="F393" s="3" t="n">
-        <v>1</v>
+        <v>0.001</v>
       </c>
       <c r="G393" s="3" t="n">
         <v>0</v>
       </c>
       <c r="H393" s="3" t="n"/>
       <c r="I393" s="3" t="n"/>
-      <c r="J393" s="3" t="n"/>
+      <c r="J393" s="3" t="inlineStr">
+        <is>
+          <t>V</t>
+        </is>
+      </c>
       <c r="K393" s="3" t="inlineStr"/>
     </row>
     <row r="394">
@@ -14762,10 +15038,18 @@
       <c r="G394" s="3" t="n">
         <v>0</v>
       </c>
-      <c r="H394" s="3" t="n"/>
-      <c r="I394" s="3" t="n"/>
+      <c r="H394" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="I394" s="3" t="n">
+        <v>1</v>
+      </c>
       <c r="J394" s="3" t="n"/>
-      <c r="K394" s="3" t="inlineStr"/>
+      <c r="K394" s="3" t="inlineStr">
+        <is>
+          <t>0=No fault detected, 1=Cell/open-wire/voltage diagnostic fault</t>
+        </is>
+      </c>
     </row>
     <row r="395">
       <c r="A395" s="3" t="inlineStr">
@@ -14795,7 +15079,11 @@
       </c>
       <c r="H395" s="3" t="n"/>
       <c r="I395" s="3" t="n"/>
-      <c r="J395" s="3" t="n"/>
+      <c r="J395" s="3" t="inlineStr">
+        <is>
+          <t>ºC</t>
+        </is>
+      </c>
       <c r="K395" s="3" t="inlineStr"/>
     </row>
     <row r="396"/>
@@ -14807,7 +15095,7 @@
       </c>
       <c r="B397" s="1" t="inlineStr">
         <is>
-          <t>ID: 0x155</t>
+          <t>ID: 0x138</t>
         </is>
       </c>
       <c r="C397" s="1" t="inlineStr">
@@ -15022,7 +15310,7 @@
       </c>
       <c r="B404" s="1" t="inlineStr">
         <is>
-          <t>ID: 0x156</t>
+          <t>ID: 0x139</t>
         </is>
       </c>
       <c r="C404" s="1" t="inlineStr">
@@ -15237,7 +15525,7 @@
       </c>
       <c r="B411" s="1" t="inlineStr">
         <is>
-          <t>ID: 0x157</t>
+          <t>ID: 0x13a</t>
         </is>
       </c>
       <c r="C411" s="1" t="inlineStr">
@@ -15452,7 +15740,7 @@
       </c>
       <c r="B418" s="1" t="inlineStr">
         <is>
-          <t>ID: 0x158</t>
+          <t>ID: 0x13b</t>
         </is>
       </c>
       <c r="C418" s="1" t="inlineStr">
@@ -15667,7 +15955,7 @@
       </c>
       <c r="B425" s="1" t="inlineStr">
         <is>
-          <t>ID: 0x159</t>
+          <t>ID: 0x13c</t>
         </is>
       </c>
       <c r="C425" s="1" t="inlineStr">
@@ -15882,7 +16170,7 @@
       </c>
       <c r="B432" s="1" t="inlineStr">
         <is>
-          <t>ID: 0x160</t>
+          <t>ID: 0x13d</t>
         </is>
       </c>
       <c r="C432" s="1" t="inlineStr">
@@ -15969,14 +16257,18 @@
         <v>0</v>
       </c>
       <c r="F434" s="3" t="n">
-        <v>1</v>
+        <v>0.001</v>
       </c>
       <c r="G434" s="3" t="n">
         <v>0</v>
       </c>
       <c r="H434" s="3" t="n"/>
       <c r="I434" s="3" t="n"/>
-      <c r="J434" s="3" t="n"/>
+      <c r="J434" s="3" t="inlineStr">
+        <is>
+          <t>V</t>
+        </is>
+      </c>
       <c r="K434" s="3" t="inlineStr"/>
     </row>
     <row r="435">
@@ -16000,14 +16292,18 @@
         <v>0</v>
       </c>
       <c r="F435" s="3" t="n">
-        <v>1</v>
+        <v>0.001</v>
       </c>
       <c r="G435" s="3" t="n">
         <v>0</v>
       </c>
       <c r="H435" s="3" t="n"/>
       <c r="I435" s="3" t="n"/>
-      <c r="J435" s="3" t="n"/>
+      <c r="J435" s="3" t="inlineStr">
+        <is>
+          <t>V</t>
+        </is>
+      </c>
       <c r="K435" s="3" t="inlineStr"/>
     </row>
     <row r="436">
@@ -16031,14 +16327,18 @@
         <v>0</v>
       </c>
       <c r="F436" s="3" t="n">
-        <v>1</v>
+        <v>0.001</v>
       </c>
       <c r="G436" s="3" t="n">
         <v>0</v>
       </c>
       <c r="H436" s="3" t="n"/>
       <c r="I436" s="3" t="n"/>
-      <c r="J436" s="3" t="n"/>
+      <c r="J436" s="3" t="inlineStr">
+        <is>
+          <t>V</t>
+        </is>
+      </c>
       <c r="K436" s="3" t="inlineStr"/>
     </row>
     <row r="437">
@@ -16062,14 +16362,18 @@
         <v>0</v>
       </c>
       <c r="F437" s="3" t="n">
-        <v>1</v>
+        <v>0.001</v>
       </c>
       <c r="G437" s="3" t="n">
         <v>0</v>
       </c>
       <c r="H437" s="3" t="n"/>
       <c r="I437" s="3" t="n"/>
-      <c r="J437" s="3" t="n"/>
+      <c r="J437" s="3" t="inlineStr">
+        <is>
+          <t>V</t>
+        </is>
+      </c>
       <c r="K437" s="3" t="inlineStr"/>
     </row>
     <row r="438"/>
@@ -16081,7 +16385,7 @@
       </c>
       <c r="B439" s="1" t="inlineStr">
         <is>
-          <t>ID: 0x161</t>
+          <t>ID: 0x13e</t>
         </is>
       </c>
       <c r="C439" s="1" t="inlineStr">
@@ -16168,14 +16472,18 @@
         <v>0</v>
       </c>
       <c r="F441" s="3" t="n">
-        <v>1</v>
+        <v>0.001</v>
       </c>
       <c r="G441" s="3" t="n">
         <v>0</v>
       </c>
       <c r="H441" s="3" t="n"/>
       <c r="I441" s="3" t="n"/>
-      <c r="J441" s="3" t="n"/>
+      <c r="J441" s="3" t="inlineStr">
+        <is>
+          <t>V</t>
+        </is>
+      </c>
       <c r="K441" s="3" t="inlineStr"/>
     </row>
     <row r="442">
@@ -16199,14 +16507,18 @@
         <v>0</v>
       </c>
       <c r="F442" s="3" t="n">
-        <v>1</v>
+        <v>0.001</v>
       </c>
       <c r="G442" s="3" t="n">
         <v>0</v>
       </c>
       <c r="H442" s="3" t="n"/>
       <c r="I442" s="3" t="n"/>
-      <c r="J442" s="3" t="n"/>
+      <c r="J442" s="3" t="inlineStr">
+        <is>
+          <t>V</t>
+        </is>
+      </c>
       <c r="K442" s="3" t="inlineStr"/>
     </row>
     <row r="443">
@@ -16235,10 +16547,18 @@
       <c r="G443" s="3" t="n">
         <v>0</v>
       </c>
-      <c r="H443" s="3" t="n"/>
-      <c r="I443" s="3" t="n"/>
+      <c r="H443" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="I443" s="3" t="n">
+        <v>1</v>
+      </c>
       <c r="J443" s="3" t="n"/>
-      <c r="K443" s="3" t="inlineStr"/>
+      <c r="K443" s="3" t="inlineStr">
+        <is>
+          <t>0=No fault detected, 1=Cell/open-wire/voltage diagnostic fault</t>
+        </is>
+      </c>
     </row>
     <row r="444">
       <c r="A444" s="3" t="inlineStr">
@@ -16268,7 +16588,11 @@
       </c>
       <c r="H444" s="3" t="n"/>
       <c r="I444" s="3" t="n"/>
-      <c r="J444" s="3" t="n"/>
+      <c r="J444" s="3" t="inlineStr">
+        <is>
+          <t>ºC</t>
+        </is>
+      </c>
       <c r="K444" s="3" t="inlineStr"/>
     </row>
     <row r="445"/>
@@ -16280,7 +16604,7 @@
       </c>
       <c r="B446" s="1" t="inlineStr">
         <is>
-          <t>ID: 0x162</t>
+          <t>ID: 0x13f</t>
         </is>
       </c>
       <c r="C446" s="1" t="inlineStr">
@@ -16495,7 +16819,7 @@
       </c>
       <c r="B453" s="1" t="inlineStr">
         <is>
-          <t>ID: 0x163</t>
+          <t>ID: 0x140</t>
         </is>
       </c>
       <c r="C453" s="1" t="inlineStr">
@@ -16710,7 +17034,7 @@
       </c>
       <c r="B460" s="1" t="inlineStr">
         <is>
-          <t>ID: 0x164</t>
+          <t>ID: 0x141</t>
         </is>
       </c>
       <c r="C460" s="1" t="inlineStr">
@@ -16925,7 +17249,7 @@
       </c>
       <c r="B467" s="1" t="inlineStr">
         <is>
-          <t>ID: 0x165</t>
+          <t>ID: 0x142</t>
         </is>
       </c>
       <c r="C467" s="1" t="inlineStr">
@@ -17140,7 +17464,7 @@
       </c>
       <c r="B474" s="1" t="inlineStr">
         <is>
-          <t>ID: 0x166</t>
+          <t>ID: 0x143</t>
         </is>
       </c>
       <c r="C474" s="1" t="inlineStr">
@@ -17355,7 +17679,7 @@
       </c>
       <c r="B481" s="1" t="inlineStr">
         <is>
-          <t>ID: 0x167</t>
+          <t>ID: 0x144</t>
         </is>
       </c>
       <c r="C481" s="1" t="inlineStr">
@@ -17442,14 +17766,18 @@
         <v>0</v>
       </c>
       <c r="F483" s="3" t="n">
-        <v>1</v>
+        <v>0.001</v>
       </c>
       <c r="G483" s="3" t="n">
         <v>0</v>
       </c>
       <c r="H483" s="3" t="n"/>
       <c r="I483" s="3" t="n"/>
-      <c r="J483" s="3" t="n"/>
+      <c r="J483" s="3" t="inlineStr">
+        <is>
+          <t>V</t>
+        </is>
+      </c>
       <c r="K483" s="3" t="inlineStr"/>
     </row>
     <row r="484">
@@ -17473,14 +17801,18 @@
         <v>0</v>
       </c>
       <c r="F484" s="3" t="n">
-        <v>1</v>
+        <v>0.001</v>
       </c>
       <c r="G484" s="3" t="n">
         <v>0</v>
       </c>
       <c r="H484" s="3" t="n"/>
       <c r="I484" s="3" t="n"/>
-      <c r="J484" s="3" t="n"/>
+      <c r="J484" s="3" t="inlineStr">
+        <is>
+          <t>V</t>
+        </is>
+      </c>
       <c r="K484" s="3" t="inlineStr"/>
     </row>
     <row r="485">
@@ -17504,14 +17836,18 @@
         <v>0</v>
       </c>
       <c r="F485" s="3" t="n">
-        <v>1</v>
+        <v>0.001</v>
       </c>
       <c r="G485" s="3" t="n">
         <v>0</v>
       </c>
       <c r="H485" s="3" t="n"/>
       <c r="I485" s="3" t="n"/>
-      <c r="J485" s="3" t="n"/>
+      <c r="J485" s="3" t="inlineStr">
+        <is>
+          <t>V</t>
+        </is>
+      </c>
       <c r="K485" s="3" t="inlineStr"/>
     </row>
     <row r="486">
@@ -17535,14 +17871,18 @@
         <v>0</v>
       </c>
       <c r="F486" s="3" t="n">
-        <v>1</v>
+        <v>0.001</v>
       </c>
       <c r="G486" s="3" t="n">
         <v>0</v>
       </c>
       <c r="H486" s="3" t="n"/>
       <c r="I486" s="3" t="n"/>
-      <c r="J486" s="3" t="n"/>
+      <c r="J486" s="3" t="inlineStr">
+        <is>
+          <t>V</t>
+        </is>
+      </c>
       <c r="K486" s="3" t="inlineStr"/>
     </row>
     <row r="487"/>
@@ -17554,7 +17894,7 @@
       </c>
       <c r="B488" s="1" t="inlineStr">
         <is>
-          <t>ID: 0x168</t>
+          <t>ID: 0x145</t>
         </is>
       </c>
       <c r="C488" s="1" t="inlineStr">
@@ -17641,14 +17981,18 @@
         <v>0</v>
       </c>
       <c r="F490" s="3" t="n">
-        <v>1</v>
+        <v>0.001</v>
       </c>
       <c r="G490" s="3" t="n">
         <v>0</v>
       </c>
       <c r="H490" s="3" t="n"/>
       <c r="I490" s="3" t="n"/>
-      <c r="J490" s="3" t="n"/>
+      <c r="J490" s="3" t="inlineStr">
+        <is>
+          <t>V</t>
+        </is>
+      </c>
       <c r="K490" s="3" t="inlineStr"/>
     </row>
     <row r="491">
@@ -17672,14 +18016,18 @@
         <v>0</v>
       </c>
       <c r="F491" s="3" t="n">
-        <v>1</v>
+        <v>0.001</v>
       </c>
       <c r="G491" s="3" t="n">
         <v>0</v>
       </c>
       <c r="H491" s="3" t="n"/>
       <c r="I491" s="3" t="n"/>
-      <c r="J491" s="3" t="n"/>
+      <c r="J491" s="3" t="inlineStr">
+        <is>
+          <t>V</t>
+        </is>
+      </c>
       <c r="K491" s="3" t="inlineStr"/>
     </row>
     <row r="492">
@@ -17708,10 +18056,18 @@
       <c r="G492" s="3" t="n">
         <v>0</v>
       </c>
-      <c r="H492" s="3" t="n"/>
-      <c r="I492" s="3" t="n"/>
+      <c r="H492" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="I492" s="3" t="n">
+        <v>1</v>
+      </c>
       <c r="J492" s="3" t="n"/>
-      <c r="K492" s="3" t="inlineStr"/>
+      <c r="K492" s="3" t="inlineStr">
+        <is>
+          <t>0=No fault detected, 1=Cell/open-wire/voltage diagnostic fault</t>
+        </is>
+      </c>
     </row>
     <row r="493">
       <c r="A493" s="3" t="inlineStr">
@@ -17741,7 +18097,11 @@
       </c>
       <c r="H493" s="3" t="n"/>
       <c r="I493" s="3" t="n"/>
-      <c r="J493" s="3" t="n"/>
+      <c r="J493" s="3" t="inlineStr">
+        <is>
+          <t>ºC</t>
+        </is>
+      </c>
       <c r="K493" s="3" t="inlineStr"/>
     </row>
     <row r="494"/>
@@ -17753,7 +18113,7 @@
       </c>
       <c r="B495" s="1" t="inlineStr">
         <is>
-          <t>ID: 0x169</t>
+          <t>ID: 0x146</t>
         </is>
       </c>
       <c r="C495" s="1" t="inlineStr">
@@ -17968,7 +18328,7 @@
       </c>
       <c r="B502" s="1" t="inlineStr">
         <is>
-          <t>ID: 0x170</t>
+          <t>ID: 0x147</t>
         </is>
       </c>
       <c r="C502" s="1" t="inlineStr">
@@ -18183,7 +18543,7 @@
       </c>
       <c r="B509" s="1" t="inlineStr">
         <is>
-          <t>ID: 0x171</t>
+          <t>ID: 0x148</t>
         </is>
       </c>
       <c r="C509" s="1" t="inlineStr">
@@ -18398,7 +18758,7 @@
       </c>
       <c r="B516" s="1" t="inlineStr">
         <is>
-          <t>ID: 0x172</t>
+          <t>ID: 0x149</t>
         </is>
       </c>
       <c r="C516" s="1" t="inlineStr">
@@ -18613,7 +18973,7 @@
       </c>
       <c r="B523" s="1" t="inlineStr">
         <is>
-          <t>ID: 0x173</t>
+          <t>ID: 0x14a</t>
         </is>
       </c>
       <c r="C523" s="1" t="inlineStr">
@@ -18828,7 +19188,7 @@
       </c>
       <c r="B530" s="1" t="inlineStr">
         <is>
-          <t>ID: 0x174</t>
+          <t>ID: 0x14b</t>
         </is>
       </c>
       <c r="C530" s="1" t="inlineStr">
@@ -18915,14 +19275,18 @@
         <v>0</v>
       </c>
       <c r="F532" s="3" t="n">
-        <v>1</v>
+        <v>0.001</v>
       </c>
       <c r="G532" s="3" t="n">
         <v>0</v>
       </c>
       <c r="H532" s="3" t="n"/>
       <c r="I532" s="3" t="n"/>
-      <c r="J532" s="3" t="n"/>
+      <c r="J532" s="3" t="inlineStr">
+        <is>
+          <t>V</t>
+        </is>
+      </c>
       <c r="K532" s="3" t="inlineStr"/>
     </row>
     <row r="533">
@@ -18946,14 +19310,18 @@
         <v>0</v>
       </c>
       <c r="F533" s="3" t="n">
-        <v>1</v>
+        <v>0.001</v>
       </c>
       <c r="G533" s="3" t="n">
         <v>0</v>
       </c>
       <c r="H533" s="3" t="n"/>
       <c r="I533" s="3" t="n"/>
-      <c r="J533" s="3" t="n"/>
+      <c r="J533" s="3" t="inlineStr">
+        <is>
+          <t>V</t>
+        </is>
+      </c>
       <c r="K533" s="3" t="inlineStr"/>
     </row>
     <row r="534">
@@ -18977,14 +19345,18 @@
         <v>0</v>
       </c>
       <c r="F534" s="3" t="n">
-        <v>1</v>
+        <v>0.001</v>
       </c>
       <c r="G534" s="3" t="n">
         <v>0</v>
       </c>
       <c r="H534" s="3" t="n"/>
       <c r="I534" s="3" t="n"/>
-      <c r="J534" s="3" t="n"/>
+      <c r="J534" s="3" t="inlineStr">
+        <is>
+          <t>V</t>
+        </is>
+      </c>
       <c r="K534" s="3" t="inlineStr"/>
     </row>
     <row r="535">
@@ -19008,14 +19380,18 @@
         <v>0</v>
       </c>
       <c r="F535" s="3" t="n">
-        <v>1</v>
+        <v>0.001</v>
       </c>
       <c r="G535" s="3" t="n">
         <v>0</v>
       </c>
       <c r="H535" s="3" t="n"/>
       <c r="I535" s="3" t="n"/>
-      <c r="J535" s="3" t="n"/>
+      <c r="J535" s="3" t="inlineStr">
+        <is>
+          <t>V</t>
+        </is>
+      </c>
       <c r="K535" s="3" t="inlineStr"/>
     </row>
     <row r="536"/>
@@ -19027,7 +19403,7 @@
       </c>
       <c r="B537" s="1" t="inlineStr">
         <is>
-          <t>ID: 0x175</t>
+          <t>ID: 0x14c</t>
         </is>
       </c>
       <c r="C537" s="1" t="inlineStr">
@@ -19114,14 +19490,18 @@
         <v>0</v>
       </c>
       <c r="F539" s="3" t="n">
-        <v>1</v>
+        <v>0.001</v>
       </c>
       <c r="G539" s="3" t="n">
         <v>0</v>
       </c>
       <c r="H539" s="3" t="n"/>
       <c r="I539" s="3" t="n"/>
-      <c r="J539" s="3" t="n"/>
+      <c r="J539" s="3" t="inlineStr">
+        <is>
+          <t>V</t>
+        </is>
+      </c>
       <c r="K539" s="3" t="inlineStr"/>
     </row>
     <row r="540">
@@ -19145,14 +19525,18 @@
         <v>0</v>
       </c>
       <c r="F540" s="3" t="n">
-        <v>1</v>
+        <v>0.001</v>
       </c>
       <c r="G540" s="3" t="n">
         <v>0</v>
       </c>
       <c r="H540" s="3" t="n"/>
       <c r="I540" s="3" t="n"/>
-      <c r="J540" s="3" t="n"/>
+      <c r="J540" s="3" t="inlineStr">
+        <is>
+          <t>V</t>
+        </is>
+      </c>
       <c r="K540" s="3" t="inlineStr"/>
     </row>
     <row r="541">
@@ -19181,10 +19565,18 @@
       <c r="G541" s="3" t="n">
         <v>0</v>
       </c>
-      <c r="H541" s="3" t="n"/>
-      <c r="I541" s="3" t="n"/>
+      <c r="H541" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="I541" s="3" t="n">
+        <v>1</v>
+      </c>
       <c r="J541" s="3" t="n"/>
-      <c r="K541" s="3" t="inlineStr"/>
+      <c r="K541" s="3" t="inlineStr">
+        <is>
+          <t>0=No fault detected, 1=Cell/open-wire/voltage diagnostic fault</t>
+        </is>
+      </c>
     </row>
     <row r="542">
       <c r="A542" s="3" t="inlineStr">
@@ -19214,7 +19606,11 @@
       </c>
       <c r="H542" s="3" t="n"/>
       <c r="I542" s="3" t="n"/>
-      <c r="J542" s="3" t="n"/>
+      <c r="J542" s="3" t="inlineStr">
+        <is>
+          <t>ºC</t>
+        </is>
+      </c>
       <c r="K542" s="3" t="inlineStr"/>
     </row>
     <row r="543"/>
@@ -19226,7 +19622,7 @@
       </c>
       <c r="B544" s="1" t="inlineStr">
         <is>
-          <t>ID: 0x176</t>
+          <t>ID: 0x14d</t>
         </is>
       </c>
       <c r="C544" s="1" t="inlineStr">
@@ -19441,7 +19837,7 @@
       </c>
       <c r="B551" s="1" t="inlineStr">
         <is>
-          <t>ID: 0x177</t>
+          <t>ID: 0x14e</t>
         </is>
       </c>
       <c r="C551" s="1" t="inlineStr">
@@ -19656,7 +20052,7 @@
       </c>
       <c r="B558" s="1" t="inlineStr">
         <is>
-          <t>ID: 0x178</t>
+          <t>ID: 0x14f</t>
         </is>
       </c>
       <c r="C558" s="1" t="inlineStr">
@@ -19871,7 +20267,7 @@
       </c>
       <c r="B565" s="1" t="inlineStr">
         <is>
-          <t>ID: 0x179</t>
+          <t>ID: 0x150</t>
         </is>
       </c>
       <c r="C565" s="1" t="inlineStr">
@@ -20086,7 +20482,7 @@
       </c>
       <c r="B572" s="1" t="inlineStr">
         <is>
-          <t>ID: 0x180</t>
+          <t>ID: 0x151</t>
         </is>
       </c>
       <c r="C572" s="1" t="inlineStr">
@@ -20301,7 +20697,7 @@
       </c>
       <c r="B579" s="1" t="inlineStr">
         <is>
-          <t>ID: 0x181</t>
+          <t>ID: 0x152</t>
         </is>
       </c>
       <c r="C579" s="1" t="inlineStr">
@@ -20388,14 +20784,18 @@
         <v>0</v>
       </c>
       <c r="F581" s="3" t="n">
-        <v>1</v>
+        <v>0.001</v>
       </c>
       <c r="G581" s="3" t="n">
         <v>0</v>
       </c>
       <c r="H581" s="3" t="n"/>
       <c r="I581" s="3" t="n"/>
-      <c r="J581" s="3" t="n"/>
+      <c r="J581" s="3" t="inlineStr">
+        <is>
+          <t>V</t>
+        </is>
+      </c>
       <c r="K581" s="3" t="inlineStr"/>
     </row>
     <row r="582">
@@ -20419,14 +20819,18 @@
         <v>0</v>
       </c>
       <c r="F582" s="3" t="n">
-        <v>1</v>
+        <v>0.001</v>
       </c>
       <c r="G582" s="3" t="n">
         <v>0</v>
       </c>
       <c r="H582" s="3" t="n"/>
       <c r="I582" s="3" t="n"/>
-      <c r="J582" s="3" t="n"/>
+      <c r="J582" s="3" t="inlineStr">
+        <is>
+          <t>V</t>
+        </is>
+      </c>
       <c r="K582" s="3" t="inlineStr"/>
     </row>
     <row r="583">
@@ -20450,14 +20854,18 @@
         <v>0</v>
       </c>
       <c r="F583" s="3" t="n">
-        <v>1</v>
+        <v>0.001</v>
       </c>
       <c r="G583" s="3" t="n">
         <v>0</v>
       </c>
       <c r="H583" s="3" t="n"/>
       <c r="I583" s="3" t="n"/>
-      <c r="J583" s="3" t="n"/>
+      <c r="J583" s="3" t="inlineStr">
+        <is>
+          <t>V</t>
+        </is>
+      </c>
       <c r="K583" s="3" t="inlineStr"/>
     </row>
     <row r="584">
@@ -20481,14 +20889,18 @@
         <v>0</v>
       </c>
       <c r="F584" s="3" t="n">
-        <v>1</v>
+        <v>0.001</v>
       </c>
       <c r="G584" s="3" t="n">
         <v>0</v>
       </c>
       <c r="H584" s="3" t="n"/>
       <c r="I584" s="3" t="n"/>
-      <c r="J584" s="3" t="n"/>
+      <c r="J584" s="3" t="inlineStr">
+        <is>
+          <t>V</t>
+        </is>
+      </c>
       <c r="K584" s="3" t="inlineStr"/>
     </row>
     <row r="585"/>
@@ -20500,7 +20912,7 @@
       </c>
       <c r="B586" s="1" t="inlineStr">
         <is>
-          <t>ID: 0x182</t>
+          <t>ID: 0x153</t>
         </is>
       </c>
       <c r="C586" s="1" t="inlineStr">
@@ -20587,14 +20999,18 @@
         <v>0</v>
       </c>
       <c r="F588" s="3" t="n">
-        <v>1</v>
+        <v>0.001</v>
       </c>
       <c r="G588" s="3" t="n">
         <v>0</v>
       </c>
       <c r="H588" s="3" t="n"/>
       <c r="I588" s="3" t="n"/>
-      <c r="J588" s="3" t="n"/>
+      <c r="J588" s="3" t="inlineStr">
+        <is>
+          <t>V</t>
+        </is>
+      </c>
       <c r="K588" s="3" t="inlineStr"/>
     </row>
     <row r="589">
@@ -20618,14 +21034,18 @@
         <v>0</v>
       </c>
       <c r="F589" s="3" t="n">
-        <v>1</v>
+        <v>0.001</v>
       </c>
       <c r="G589" s="3" t="n">
         <v>0</v>
       </c>
       <c r="H589" s="3" t="n"/>
       <c r="I589" s="3" t="n"/>
-      <c r="J589" s="3" t="n"/>
+      <c r="J589" s="3" t="inlineStr">
+        <is>
+          <t>V</t>
+        </is>
+      </c>
       <c r="K589" s="3" t="inlineStr"/>
     </row>
     <row r="590">
@@ -20654,10 +21074,18 @@
       <c r="G590" s="3" t="n">
         <v>0</v>
       </c>
-      <c r="H590" s="3" t="n"/>
-      <c r="I590" s="3" t="n"/>
+      <c r="H590" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="I590" s="3" t="n">
+        <v>1</v>
+      </c>
       <c r="J590" s="3" t="n"/>
-      <c r="K590" s="3" t="inlineStr"/>
+      <c r="K590" s="3" t="inlineStr">
+        <is>
+          <t>0=No fault detected, 1=Cell/open-wire/voltage diagnostic fault</t>
+        </is>
+      </c>
     </row>
     <row r="591">
       <c r="A591" s="3" t="inlineStr">
@@ -20687,7 +21115,11 @@
       </c>
       <c r="H591" s="3" t="n"/>
       <c r="I591" s="3" t="n"/>
-      <c r="J591" s="3" t="n"/>
+      <c r="J591" s="3" t="inlineStr">
+        <is>
+          <t>ºC</t>
+        </is>
+      </c>
       <c r="K591" s="3" t="inlineStr"/>
     </row>
     <row r="592"/>

--- a/dbc_signals.xlsx
+++ b/dbc_signals.xlsx
@@ -2889,7 +2889,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K597"/>
+  <dimension ref="A1:K607"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="36" customWidth="1" min="1" max="1"/>
@@ -2902,7 +2902,7 @@
     <col width="5" customWidth="1" min="8" max="8"/>
     <col width="7" customWidth="1" min="9" max="9"/>
     <col width="8" customWidth="1" min="10" max="10"/>
-    <col width="64" customWidth="1" min="11" max="11"/>
+    <col width="260" customWidth="1" min="11" max="11"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -21305,6 +21305,330 @@
         </is>
       </c>
       <c r="K597" s="3" t="inlineStr"/>
+    </row>
+    <row r="598">
+      <c r="A598" s="3" t="inlineStr">
+        <is>
+          <t>master_firmware_version</t>
+        </is>
+      </c>
+      <c r="B598" s="3" t="n">
+        <v>32</v>
+      </c>
+      <c r="C598" s="3" t="n">
+        <v>6</v>
+      </c>
+      <c r="D598" s="3" t="inlineStr">
+        <is>
+          <t>Intel</t>
+        </is>
+      </c>
+      <c r="E598" s="3" t="b">
+        <v>0</v>
+      </c>
+      <c r="F598" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="G598" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="H598" s="3" t="n"/>
+      <c r="I598" s="3" t="n"/>
+      <c r="J598" s="3" t="n"/>
+      <c r="K598" s="3" t="inlineStr">
+        <is>
+          <t>0=Unknown Firmware, 1=alpha, 3=beta, 5=alpha-v1, 7=beta-v1, 9=alpha-v2, 13=alpha-v3, 17=alpha-v3.1, 11=beta-v2, 15=beta-v3</t>
+        </is>
+      </c>
+    </row>
+    <row r="599">
+      <c r="A599" s="3" t="inlineStr">
+        <is>
+          <t>master_fan_pwm</t>
+        </is>
+      </c>
+      <c r="B599" s="3" t="n">
+        <v>40</v>
+      </c>
+      <c r="C599" s="3" t="n">
+        <v>8</v>
+      </c>
+      <c r="D599" s="3" t="inlineStr">
+        <is>
+          <t>Intel</t>
+        </is>
+      </c>
+      <c r="E599" s="3" t="b">
+        <v>0</v>
+      </c>
+      <c r="F599" s="3" t="n">
+        <v>0.392</v>
+      </c>
+      <c r="G599" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="H599" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="I599" s="3" t="n">
+        <v>100</v>
+      </c>
+      <c r="J599" s="3" t="inlineStr">
+        <is>
+          <t>PWM</t>
+        </is>
+      </c>
+      <c r="K599" s="3" t="inlineStr"/>
+    </row>
+    <row r="600"/>
+    <row r="601">
+      <c r="A601" s="1" t="inlineStr">
+        <is>
+          <t>Message: Master_PreCharge_ID_1</t>
+        </is>
+      </c>
+      <c r="B601" s="1" t="inlineStr">
+        <is>
+          <t>ID: 0x702</t>
+        </is>
+      </c>
+      <c r="C601" s="1" t="inlineStr">
+        <is>
+          <t>Sender(s): AMS</t>
+        </is>
+      </c>
+    </row>
+    <row r="602">
+      <c r="A602" s="2" t="inlineStr">
+        <is>
+          <t>Signal Name</t>
+        </is>
+      </c>
+      <c r="B602" s="2" t="inlineStr">
+        <is>
+          <t>Start Bit</t>
+        </is>
+      </c>
+      <c r="C602" s="2" t="inlineStr">
+        <is>
+          <t>Length (bits)</t>
+        </is>
+      </c>
+      <c r="D602" s="2" t="inlineStr">
+        <is>
+          <t>Byte Order</t>
+        </is>
+      </c>
+      <c r="E602" s="2" t="inlineStr">
+        <is>
+          <t>Signed</t>
+        </is>
+      </c>
+      <c r="F602" s="2" t="inlineStr">
+        <is>
+          <t>Factor</t>
+        </is>
+      </c>
+      <c r="G602" s="2" t="inlineStr">
+        <is>
+          <t>Offset</t>
+        </is>
+      </c>
+      <c r="H602" s="2" t="inlineStr">
+        <is>
+          <t>Min</t>
+        </is>
+      </c>
+      <c r="I602" s="2" t="inlineStr">
+        <is>
+          <t>Max</t>
+        </is>
+      </c>
+      <c r="J602" s="2" t="inlineStr">
+        <is>
+          <t>Unit</t>
+        </is>
+      </c>
+      <c r="K602" s="2" t="inlineStr">
+        <is>
+          <t>Choices</t>
+        </is>
+      </c>
+    </row>
+    <row r="603">
+      <c r="A603" s="3" t="inlineStr">
+        <is>
+          <t>precharge_ctc_air_pos_state</t>
+        </is>
+      </c>
+      <c r="B603" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="C603" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="D603" s="3" t="inlineStr">
+        <is>
+          <t>Intel</t>
+        </is>
+      </c>
+      <c r="E603" s="3" t="b">
+        <v>0</v>
+      </c>
+      <c r="F603" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="G603" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="H603" s="3" t="n"/>
+      <c r="I603" s="3" t="n"/>
+      <c r="J603" s="3" t="inlineStr">
+        <is>
+          <t>ON/OFF</t>
+        </is>
+      </c>
+      <c r="K603" s="3" t="inlineStr"/>
+    </row>
+    <row r="604">
+      <c r="A604" s="3" t="inlineStr">
+        <is>
+          <t>precharge_ctc_air_min_state</t>
+        </is>
+      </c>
+      <c r="B604" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="C604" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="D604" s="3" t="inlineStr">
+        <is>
+          <t>Intel</t>
+        </is>
+      </c>
+      <c r="E604" s="3" t="b">
+        <v>0</v>
+      </c>
+      <c r="F604" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="G604" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="H604" s="3" t="n"/>
+      <c r="I604" s="3" t="n"/>
+      <c r="J604" s="3" t="inlineStr">
+        <is>
+          <t>ON/OFF</t>
+        </is>
+      </c>
+      <c r="K604" s="3" t="inlineStr"/>
+    </row>
+    <row r="605">
+      <c r="A605" s="3" t="inlineStr">
+        <is>
+          <t>precharge_ctc_charge_state</t>
+        </is>
+      </c>
+      <c r="B605" s="3" t="n">
+        <v>2</v>
+      </c>
+      <c r="C605" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="D605" s="3" t="inlineStr">
+        <is>
+          <t>Intel</t>
+        </is>
+      </c>
+      <c r="E605" s="3" t="b">
+        <v>0</v>
+      </c>
+      <c r="F605" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="G605" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="H605" s="3" t="n"/>
+      <c r="I605" s="3" t="n"/>
+      <c r="J605" s="3" t="inlineStr">
+        <is>
+          <t>ON/OFF</t>
+        </is>
+      </c>
+      <c r="K605" s="3" t="inlineStr"/>
+    </row>
+    <row r="606">
+      <c r="A606" s="3" t="inlineStr">
+        <is>
+          <t>precharge_ctc_discharge_state</t>
+        </is>
+      </c>
+      <c r="B606" s="3" t="n">
+        <v>3</v>
+      </c>
+      <c r="C606" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="D606" s="3" t="inlineStr">
+        <is>
+          <t>Intel</t>
+        </is>
+      </c>
+      <c r="E606" s="3" t="b">
+        <v>0</v>
+      </c>
+      <c r="F606" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="G606" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="H606" s="3" t="n"/>
+      <c r="I606" s="3" t="n"/>
+      <c r="J606" s="3" t="inlineStr">
+        <is>
+          <t>ON/OFF</t>
+        </is>
+      </c>
+      <c r="K606" s="3" t="inlineStr"/>
+    </row>
+    <row r="607">
+      <c r="A607" s="3" t="inlineStr">
+        <is>
+          <t>precharge_state</t>
+        </is>
+      </c>
+      <c r="B607" s="3" t="n">
+        <v>8</v>
+      </c>
+      <c r="C607" s="3" t="n">
+        <v>6</v>
+      </c>
+      <c r="D607" s="3" t="inlineStr">
+        <is>
+          <t>Intel</t>
+        </is>
+      </c>
+      <c r="E607" s="3" t="b">
+        <v>0</v>
+      </c>
+      <c r="F607" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="G607" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="H607" s="3" t="n"/>
+      <c r="I607" s="3" t="n"/>
+      <c r="J607" s="3" t="n"/>
+      <c r="K607" s="3" t="inlineStr">
+        <is>
+          <t>0=START, 1=OPEN_ALL, 2=SWITCH_HVNEG, 3=DELAY1, 4=VERIFY1, 5=SWITCH_PRECHARGE, 6=DELAY2, 7=VERIFY2, 8=VERIFY_CURRENT, 9=VERIFY_BUS_VOLT, 10=SWITCH_HVPOS, 11=DELAY3, 12=VERIFY3, 13=TURN_OFF_PRECHARGE, 14=DELAY4, 15=VERIFY4, 16=END, 17=WRONG, 18=KILL, 19=RX_CAN</t>
+        </is>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/dbc_signals.xlsx
+++ b/dbc_signals.xlsx
@@ -2889,7 +2889,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K607"/>
+  <dimension ref="A1:K608"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="36" customWidth="1" min="1" max="1"/>
@@ -21380,124 +21380,124 @@
       </c>
       <c r="K599" s="3" t="inlineStr"/>
     </row>
-    <row r="600"/>
-    <row r="601">
-      <c r="A601" s="1" t="inlineStr">
+    <row r="600">
+      <c r="A600" s="3" t="inlineStr">
+        <is>
+          <t>master_state</t>
+        </is>
+      </c>
+      <c r="B600" s="3" t="n">
+        <v>48</v>
+      </c>
+      <c r="C600" s="3" t="n">
+        <v>6</v>
+      </c>
+      <c r="D600" s="3" t="inlineStr">
+        <is>
+          <t>Intel</t>
+        </is>
+      </c>
+      <c r="E600" s="3" t="b">
+        <v>0</v>
+      </c>
+      <c r="F600" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="G600" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="H600" s="3" t="n"/>
+      <c r="I600" s="3" t="n"/>
+      <c r="J600" s="3" t="n"/>
+      <c r="K600" s="3" t="inlineStr">
+        <is>
+          <t>0=BALANCING, 1=CHARGING, 2=IDLE, 3=ONMISSION, 4=STARTUP, 5=DISCHARGE_TEST, 6=RESET_ISA, 7=FAULT</t>
+        </is>
+      </c>
+    </row>
+    <row r="601"/>
+    <row r="602">
+      <c r="A602" s="1" t="inlineStr">
         <is>
           <t>Message: Master_PreCharge_ID_1</t>
         </is>
       </c>
-      <c r="B601" s="1" t="inlineStr">
+      <c r="B602" s="1" t="inlineStr">
         <is>
           <t>ID: 0x702</t>
         </is>
       </c>
-      <c r="C601" s="1" t="inlineStr">
+      <c r="C602" s="1" t="inlineStr">
         <is>
           <t>Sender(s): AMS</t>
         </is>
       </c>
     </row>
-    <row r="602">
-      <c r="A602" s="2" t="inlineStr">
+    <row r="603">
+      <c r="A603" s="2" t="inlineStr">
         <is>
           <t>Signal Name</t>
         </is>
       </c>
-      <c r="B602" s="2" t="inlineStr">
+      <c r="B603" s="2" t="inlineStr">
         <is>
           <t>Start Bit</t>
         </is>
       </c>
-      <c r="C602" s="2" t="inlineStr">
+      <c r="C603" s="2" t="inlineStr">
         <is>
           <t>Length (bits)</t>
         </is>
       </c>
-      <c r="D602" s="2" t="inlineStr">
+      <c r="D603" s="2" t="inlineStr">
         <is>
           <t>Byte Order</t>
         </is>
       </c>
-      <c r="E602" s="2" t="inlineStr">
+      <c r="E603" s="2" t="inlineStr">
         <is>
           <t>Signed</t>
         </is>
       </c>
-      <c r="F602" s="2" t="inlineStr">
+      <c r="F603" s="2" t="inlineStr">
         <is>
           <t>Factor</t>
         </is>
       </c>
-      <c r="G602" s="2" t="inlineStr">
+      <c r="G603" s="2" t="inlineStr">
         <is>
           <t>Offset</t>
         </is>
       </c>
-      <c r="H602" s="2" t="inlineStr">
+      <c r="H603" s="2" t="inlineStr">
         <is>
           <t>Min</t>
         </is>
       </c>
-      <c r="I602" s="2" t="inlineStr">
+      <c r="I603" s="2" t="inlineStr">
         <is>
           <t>Max</t>
         </is>
       </c>
-      <c r="J602" s="2" t="inlineStr">
+      <c r="J603" s="2" t="inlineStr">
         <is>
           <t>Unit</t>
         </is>
       </c>
-      <c r="K602" s="2" t="inlineStr">
+      <c r="K603" s="2" t="inlineStr">
         <is>
           <t>Choices</t>
         </is>
       </c>
-    </row>
-    <row r="603">
-      <c r="A603" s="3" t="inlineStr">
-        <is>
-          <t>precharge_ctc_air_pos_state</t>
-        </is>
-      </c>
-      <c r="B603" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="C603" s="3" t="n">
-        <v>1</v>
-      </c>
-      <c r="D603" s="3" t="inlineStr">
-        <is>
-          <t>Intel</t>
-        </is>
-      </c>
-      <c r="E603" s="3" t="b">
-        <v>0</v>
-      </c>
-      <c r="F603" s="3" t="n">
-        <v>1</v>
-      </c>
-      <c r="G603" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="H603" s="3" t="n"/>
-      <c r="I603" s="3" t="n"/>
-      <c r="J603" s="3" t="inlineStr">
-        <is>
-          <t>ON/OFF</t>
-        </is>
-      </c>
-      <c r="K603" s="3" t="inlineStr"/>
     </row>
     <row r="604">
       <c r="A604" s="3" t="inlineStr">
         <is>
-          <t>precharge_ctc_air_min_state</t>
+          <t>precharge_ctc_air_pos_state</t>
         </is>
       </c>
       <c r="B604" s="3" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="C604" s="3" t="n">
         <v>1</v>
@@ -21528,11 +21528,11 @@
     <row r="605">
       <c r="A605" s="3" t="inlineStr">
         <is>
-          <t>precharge_ctc_charge_state</t>
+          <t>precharge_ctc_air_min_state</t>
         </is>
       </c>
       <c r="B605" s="3" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C605" s="3" t="n">
         <v>1</v>
@@ -21563,11 +21563,11 @@
     <row r="606">
       <c r="A606" s="3" t="inlineStr">
         <is>
-          <t>precharge_ctc_discharge_state</t>
+          <t>precharge_ctc_charge_state</t>
         </is>
       </c>
       <c r="B606" s="3" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="C606" s="3" t="n">
         <v>1</v>
@@ -21598,14 +21598,14 @@
     <row r="607">
       <c r="A607" s="3" t="inlineStr">
         <is>
-          <t>precharge_state</t>
+          <t>precharge_ctc_discharge_state</t>
         </is>
       </c>
       <c r="B607" s="3" t="n">
-        <v>8</v>
+        <v>3</v>
       </c>
       <c r="C607" s="3" t="n">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="D607" s="3" t="inlineStr">
         <is>
@@ -21623,8 +21623,43 @@
       </c>
       <c r="H607" s="3" t="n"/>
       <c r="I607" s="3" t="n"/>
-      <c r="J607" s="3" t="n"/>
-      <c r="K607" s="3" t="inlineStr">
+      <c r="J607" s="3" t="inlineStr">
+        <is>
+          <t>ON/OFF</t>
+        </is>
+      </c>
+      <c r="K607" s="3" t="inlineStr"/>
+    </row>
+    <row r="608">
+      <c r="A608" s="3" t="inlineStr">
+        <is>
+          <t>precharge_state</t>
+        </is>
+      </c>
+      <c r="B608" s="3" t="n">
+        <v>8</v>
+      </c>
+      <c r="C608" s="3" t="n">
+        <v>6</v>
+      </c>
+      <c r="D608" s="3" t="inlineStr">
+        <is>
+          <t>Intel</t>
+        </is>
+      </c>
+      <c r="E608" s="3" t="b">
+        <v>0</v>
+      </c>
+      <c r="F608" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="G608" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="H608" s="3" t="n"/>
+      <c r="I608" s="3" t="n"/>
+      <c r="J608" s="3" t="n"/>
+      <c r="K608" s="3" t="inlineStr">
         <is>
           <t>0=START, 1=OPEN_ALL, 2=SWITCH_HVNEG, 3=DELAY1, 4=VERIFY1, 5=SWITCH_PRECHARGE, 6=DELAY2, 7=VERIFY2, 8=VERIFY_CURRENT, 9=VERIFY_BUS_VOLT, 10=SWITCH_HVPOS, 11=DELAY3, 12=VERIFY3, 13=TURN_OFF_PRECHARGE, 14=DELAY4, 15=VERIFY4, 16=END, 17=WRONG, 18=KILL, 19=RX_CAN</t>
         </is>
